--- a/backend/data/financials_by_company/000635.SZ.xlsx
+++ b/backend/data/financials_by_company/000635.SZ.xlsx
@@ -3630,182 +3630,182 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -3907,28 +3907,28 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>6.53</v>
+        <v>6.27</v>
       </c>
       <c r="U2" t="n">
-        <v>6.75</v>
+        <v>6.24</v>
       </c>
       <c r="V2" t="n">
-        <v>6.37</v>
+        <v>6.16</v>
       </c>
       <c r="W2" t="n">
-        <v>6.73</v>
+        <v>6.35</v>
       </c>
       <c r="X2" t="n">
-        <v>6.53</v>
+        <v>6.27</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.75</v>
+        <v>6.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.37</v>
+        <v>6.16</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.73</v>
+        <v>6.35</v>
       </c>
       <c r="AB2" t="n">
         <v>1624406400</v>
@@ -3937,25 +3937,25 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>8025010</v>
+        <v>6794362</v>
       </c>
       <c r="AE2" t="n">
-        <v>8025010</v>
+        <v>6794362</v>
       </c>
       <c r="AF2" t="n">
-        <v>7569693</v>
+        <v>7302767</v>
       </c>
       <c r="AG2" t="n">
-        <v>10758232</v>
+        <v>7172124</v>
       </c>
       <c r="AH2" t="n">
-        <v>10758232</v>
+        <v>7172124</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.7</v>
+        <v>6.19</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6.71</v>
+        <v>6.2</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -3964,13 +3964,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2640695296</v>
+        <v>2439687168</v>
       </c>
       <c r="AN2" t="n">
-        <v>2573692558</v>
+        <v>2431804453</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.37</v>
+        <v>5.95</v>
       </c>
       <c r="AP2" t="n">
         <v>10.93</v>
@@ -3982,13 +3982,13 @@
         <v>3.159041</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.5445938</v>
+        <v>1.4270203</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6556</v>
+        <v>7.3218</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.784599999999999</v>
+        <v>8.687250000000001</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3001964544</v>
+        <v>2800956416</v>
       </c>
       <c r="BA2" t="n">
         <v>-0.32379</v>
@@ -4017,10 +4017,10 @@
         <v>394133623</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.51060003</v>
+        <v>0.49618</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.07831</v>
+        <v>0.04802</v>
       </c>
       <c r="BF2" t="n">
         <v>394133623</v>
@@ -4029,7 +4029,7 @@
         <v>2.798</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.3945675</v>
+        <v>2.2122943</v>
       </c>
       <c r="BI2" t="n">
         <v>1767139200</v>
@@ -4055,16 +4055,16 @@
         <v>1132617600</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.756</v>
+        <v>1.638</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-13.088</v>
+        <v>-12.212</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.24245942</v>
+        <v>-0.2962963</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BT2" t="n">
         <v>0.14</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>6.7</v>
+        <v>6.19</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4177,137 +4177,137 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CY2" t="n">
-        <v>2.6033628</v>
+      <c r="CY2" t="b">
+        <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>848453400000</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-0.07999992</v>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>NINGXIA YOUNGLIGHT CHEMICALS CO</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.1699996</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>6.37 - 6.73</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
+          <t>6.16 - 6.35</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
+      <c r="DD2" t="n">
+        <v>7302767</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.24000025</v>
+      </c>
       <c r="DF2" t="n">
-        <v>7569693</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.32999992</v>
+        <v>0.040336177</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>5.95 - 10.93</t>
+        </is>
       </c>
       <c r="DH2" t="n">
-        <v>0.051805325</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>6.37 - 10.93</t>
-        </is>
+        <v>-4.7400002</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.43366882</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-4.2300005</v>
+        <v>-29.62963</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0.38700828</v>
+        <v>1619521140</v>
       </c>
       <c r="DL2" t="n">
-        <v>-24.245941</v>
+        <v>1619521140</v>
       </c>
       <c r="DM2" t="n">
-        <v>1619521140</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>1619521140</v>
+        <v>-1.68</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DO2" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.95560026</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.12482369</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-2.0846004</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.23730169</v>
+        <v>1783062273</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>finmb_11168502</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
       </c>
       <c r="DT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
+        <v>28800000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
       </c>
       <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DW2" t="b">
+      <c r="DW2" t="n">
+        <v>-1.1318002</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.15457949</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-2.49725</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.28746152</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EC2" t="b">
         <v>0</v>
       </c>
-      <c r="DX2" t="n">
-        <v>848453400000</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1782111852</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>finmb_11168502</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>28800000</v>
+          <t>NINGXIA YOUNGLIGHT CHEMICALS CO</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>Ningxia Yinglite Chemicals Co., Ltd</t>
+        </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Ningxia Yinglite Chemicals Co., Ltd</t>
-        </is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EG2" t="n">
+        <v>-1.2759159</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>6.19</v>
       </c>
       <c r="EI2" t="inlineStr"/>
     </row>
